--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:09:55+00:00</t>
+    <t>2023-05-26T15:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1035,6 +1035,77 @@
     <t>http://openhie.org/fhir/training-solution-1/ValueSet/vs-careplan-outcome</t>
   </si>
   <si>
+    <t>CarePlan.activity.outcomeCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>Interruptions in treatment</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>CarePlan.activity.outcomeReference</t>
   </si>
   <si>
@@ -1135,13 +1206,6 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>CarePlan.activity.detail.extension:artRegimenSwitchedOrSubstituted</t>
   </si>
   <si>
@@ -1267,6 +1331,21 @@
     <t>OBR-4 / RXE-2 / RXO-1 / RXD-2</t>
   </si>
   <si>
+    <t>CarePlan.activity.detail.code.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.code.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.code.coding</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.code.text</t>
+  </si>
+  <si>
+    <t>ARV medication request</t>
+  </si>
+  <si>
     <t>CarePlan.activity.detail.reasonCode</t>
   </si>
   <si>
@@ -1501,6 +1580,33 @@
   </si>
   <si>
     <t>http://openhie.org/fhir/training-solution-1/ValueSet/vs-arv-regimen</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.product[x]:productCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.product[x].id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.product[x]:productCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.product[x].extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.product[x]:productCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.product[x].coding</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.product[x]:productCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.product[x].text</t>
+  </si>
+  <si>
+    <t>ARV Regimen</t>
   </si>
   <si>
     <t>CarePlan.activity.detail.dailyAmount</t>
@@ -1893,11 +1999,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="64.3359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="65.95703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.953125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="32.90625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1924,7 +2030,7 @@
     <col min="26" max="26" width="75.31640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="42.671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -6071,7 +6177,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -6083,20 +6189,16 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>287</v>
+        <v>213</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6144,25 +6246,25 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -6173,14 +6275,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6199,20 +6301,18 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>334</v>
+        <v>133</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>335</v>
+        <v>134</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6248,19 +6348,19 @@
         <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>80</v>
+        <v>329</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6272,27 +6372,27 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>340</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6303,7 +6403,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6312,22 +6412,22 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6376,39 +6476,39 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6422,26 +6522,28 @@
         <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J40" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K40" t="s" s="2">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6451,7 +6553,7 @@
         <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>80</v>
@@ -6490,7 +6592,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6499,7 +6601,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -6508,21 +6610,21 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6533,7 +6635,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6545,16 +6647,20 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -6602,25 +6708,25 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6631,10 +6737,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6657,16 +6763,20 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6702,17 +6812,19 @@
         <v>80</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6724,31 +6836,29 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>80</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6760,7 +6870,7 @@
         <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>80</v>
@@ -6769,16 +6879,20 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6826,25 +6940,25 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -6855,14 +6969,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>80</v>
       </c>
@@ -6883,16 +6995,18 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -6940,25 +7054,25 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>80</v>
+        <v>376</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -6969,14 +7083,12 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>80</v>
       </c>
@@ -6988,7 +7100,7 @@
         <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>80</v>
@@ -6997,13 +7109,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>373</v>
+        <v>213</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>374</v>
+        <v>309</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7054,25 +7166,25 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>365</v>
+        <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -7083,14 +7195,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7103,26 +7215,22 @@
         <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7158,19 +7266,17 @@
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7188,7 +7294,7 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7199,12 +7305,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7225,18 +7333,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>383</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7245,7 +7351,7 @@
         <v>80</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>80</v>
@@ -7260,13 +7366,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7284,25 +7390,25 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>315</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>384</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7313,12 +7419,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7327,10 +7435,10 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
@@ -7339,18 +7447,16 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>156</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>388</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7398,7 +7504,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7407,16 +7513,16 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
@@ -7427,12 +7533,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7441,10 +7549,10 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
@@ -7453,20 +7561,16 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>101</v>
+        <v>394</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>161</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7514,7 +7618,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>315</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7523,16 +7627,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
@@ -7543,45 +7647,45 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I50" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I50" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>203</v>
+        <v>133</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>392</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>394</v>
+        <v>136</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>395</v>
+        <v>142</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7606,11 +7710,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>396</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7628,39 +7734,39 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>320</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>398</v>
+        <v>130</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>399</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7671,10 +7777,10 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
@@ -7683,18 +7789,18 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7703,7 +7809,7 @@
         <v>80</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>80</v>
@@ -7718,14 +7824,14 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>405</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7742,13 +7848,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -7757,10 +7863,10 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>406</v>
+        <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>405</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
@@ -7771,10 +7877,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7797,18 +7903,18 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -7856,7 +7962,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7871,10 +7977,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>282</v>
+        <v>158</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -7885,10 +7991,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7911,17 +8017,19 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>294</v>
+        <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>161</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -7970,7 +8078,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7985,10 +8093,10 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>299</v>
+        <v>159</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -7999,10 +8107,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8010,34 +8118,34 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8064,11 +8172,9 @@
       <c r="X54" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y54" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8086,10 +8192,10 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>87</v>
@@ -8101,24 +8207,24 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8141,17 +8247,15 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>427</v>
+        <v>309</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8200,7 +8304,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>426</v>
+        <v>311</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8212,13 +8316,13 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8229,52 +8333,48 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>432</v>
+        <v>133</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>433</v>
+        <v>134</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>434</v>
+        <v>314</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q56" t="s" s="2">
-        <v>437</v>
-      </c>
+      <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8306,37 +8406,37 @@
         <v>80</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>80</v>
+        <v>329</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>315</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>439</v>
+        <v>312</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
@@ -8347,10 +8447,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8361,7 +8461,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -8370,20 +8470,22 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>441</v>
+        <v>332</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>442</v>
+        <v>333</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>444</v>
+        <v>336</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8420,23 +8522,25 @@
         <v>80</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
@@ -8445,28 +8549,26 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>247</v>
+        <v>338</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>446</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8478,26 +8580,28 @@
         <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>442</v>
+        <v>341</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>444</v>
+        <v>344</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8507,7 +8611,7 @@
         <v>80</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>80</v>
+        <v>425</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>80</v>
@@ -8546,7 +8650,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>440</v>
+        <v>346</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8561,24 +8665,24 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>247</v>
+        <v>347</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>446</v>
+        <v>348</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8589,7 +8693,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -8601,20 +8705,18 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>450</v>
+        <v>203</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8638,13 +8740,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>80</v>
+        <v>430</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -8662,13 +8764,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -8677,24 +8779,24 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>80</v>
+        <v>432</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>456</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8717,20 +8819,18 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8778,7 +8878,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8793,24 +8893,24 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>462</v>
+        <v>282</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>463</v>
+        <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8821,7 +8921,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -8833,16 +8933,18 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>466</v>
+        <v>294</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>439</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8866,35 +8968,37 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>469</v>
+        <v>80</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AC61" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -8906,55 +9010,57 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>471</v>
+        <v>299</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I62" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I62" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -8980,9 +9086,11 @@
       <c r="X62" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y62" s="2"/>
+      <c r="Y62" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9000,10 +9108,10 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>87</v>
@@ -9015,28 +9123,28 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>472</v>
+        <v>451</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>477</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9055,18 +9163,18 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>478</v>
+        <v>203</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9114,7 +9222,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9129,24 +9237,24 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>80</v>
+        <v>456</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>482</v>
+        <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>483</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9163,26 +9271,32 @@
         <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="R64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9226,7 +9340,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9241,24 +9355,24 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>488</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9281,16 +9395,18 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>213</v>
+        <v>467</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -9326,19 +9442,17 @@
         <v>80</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9353,26 +9467,28 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>492</v>
+        <v>247</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>340</v>
+        <v>472</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>80</v>
       </c>
@@ -9381,7 +9497,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>88</v>
@@ -9393,17 +9509,17 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>334</v>
+        <v>241</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9452,13 +9568,13 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
@@ -9467,20 +9583,1384 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AC69" s="2"/>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y70" s="2"/>
+      <c r="Z70" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>340</v>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN66">
+  <autoFilter ref="A1:AN78">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9490,7 +10970,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:10:57+00:00</t>
+    <t>2023-05-29T05:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:56:41+00:00</t>
+    <t>2023-06-20T13:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
